--- a/Pruebas calificadas/COLEGIO SANTIAGO DE LAS ATALAYAS-701_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO SANTIAGO DE LAS ATALAYAS-701_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -819,7 +815,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -1072,7 +1064,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -1325,7 +1313,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1566,11 +1554,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -1578,7 +1562,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1819,11 +1803,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -1831,7 +1811,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2064,11 +2044,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -2076,7 +2052,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2317,11 +2293,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -2329,7 +2301,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2570,11 +2542,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -2582,7 +2550,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2823,11 +2791,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -2835,7 +2799,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3076,11 +3040,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -3088,7 +3048,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3329,11 +3289,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -3341,7 +3297,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3582,11 +3538,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -3594,7 +3546,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3835,11 +3787,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -3847,7 +3795,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4088,11 +4036,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -4100,7 +4044,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4341,11 +4285,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -4353,7 +4293,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4594,11 +4534,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -4606,7 +4542,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4847,11 +4783,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -4859,7 +4791,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5100,11 +5032,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -5112,7 +5040,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5353,11 +5281,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -5365,7 +5289,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5606,11 +5530,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -5618,7 +5538,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5859,11 +5779,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -5871,7 +5787,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6112,11 +6028,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -6124,7 +6036,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6365,11 +6277,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -6377,7 +6285,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6618,11 +6526,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -6630,7 +6534,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6871,11 +6775,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -6883,7 +6783,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7124,11 +7024,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -7136,7 +7032,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7373,11 +7269,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -7385,7 +7277,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7626,11 +7518,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -7638,7 +7526,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7879,11 +7767,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -7891,7 +7775,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8132,11 +8016,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -8144,7 +8024,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8385,11 +8265,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -8397,7 +8273,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8638,11 +8514,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -8650,7 +8522,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8891,11 +8763,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -8903,7 +8771,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9144,11 +9012,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -9156,7 +9020,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9397,11 +9261,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -9409,7 +9269,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9650,11 +9510,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -9662,7 +9518,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9903,11 +9759,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -9915,7 +9767,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10156,11 +10008,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -10168,7 +10016,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10409,11 +10257,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -10421,7 +10265,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10662,11 +10506,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -10674,7 +10514,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -10915,11 +10755,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -10927,7 +10763,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -11168,11 +11004,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -11180,7 +11012,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -11421,11 +11253,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -11433,7 +11261,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -11674,11 +11502,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -11686,7 +11510,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -11927,11 +11751,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -11939,7 +11759,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -12180,11 +12000,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -12192,7 +12008,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -12433,11 +12249,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -12445,7 +12257,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -12686,11 +12498,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -12698,7 +12506,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -12939,11 +12747,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -12951,7 +12755,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -13192,11 +12996,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -13204,7 +13004,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -13445,11 +13245,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -13457,7 +13253,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -13698,11 +13494,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -13710,7 +13502,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -13943,11 +13735,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -13955,7 +13743,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -14196,11 +13984,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -14208,7 +13992,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -14449,11 +14233,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -14461,7 +14241,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -14694,11 +14474,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -14706,7 +14482,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -14947,11 +14723,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -14959,7 +14731,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -15200,11 +14972,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -15212,7 +14980,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -15449,11 +15217,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -15461,7 +15225,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -15702,11 +15466,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -15714,7 +15474,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -15955,11 +15715,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -15967,7 +15723,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -16208,11 +15964,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -16220,7 +15972,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -16461,11 +16213,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -16473,7 +16221,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -16662,11 +16410,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -16674,7 +16418,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -16915,11 +16659,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="inlineStr"/>
       <c r="B66" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -16927,7 +16667,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -17168,11 +16908,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -17180,7 +16916,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -17409,11 +17145,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="inlineStr"/>
       <c r="B68" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -17421,7 +17153,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -17658,11 +17390,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="inlineStr"/>
       <c r="B69" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -17670,7 +17398,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -17859,11 +17587,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A70" s="2" t="inlineStr"/>
       <c r="B70" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -17871,7 +17595,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -18112,11 +17836,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A71" s="2" t="inlineStr"/>
       <c r="B71" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -18124,7 +17844,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -18365,11 +18085,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A72" s="2" t="inlineStr"/>
       <c r="B72" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -18377,7 +18093,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -18618,11 +18334,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A73" s="2" t="inlineStr"/>
       <c r="B73" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -18630,7 +18342,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -18871,11 +18583,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A74" s="2" t="inlineStr"/>
       <c r="B74" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -18883,7 +18591,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -19124,11 +18832,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A75" s="2" t="inlineStr"/>
       <c r="B75" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -19136,7 +18840,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -19377,11 +19081,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A76" s="2" t="inlineStr"/>
       <c r="B76" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -19389,7 +19089,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -19630,11 +19330,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A77" s="2" t="inlineStr"/>
       <c r="B77" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -19642,7 +19338,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -19875,11 +19571,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A78" s="2" t="inlineStr"/>
       <c r="B78" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -19887,7 +19579,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -20128,11 +19820,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A79" s="2" t="inlineStr"/>
       <c r="B79" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -20140,7 +19828,7 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -20381,11 +20069,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A80" s="2" t="inlineStr"/>
       <c r="B80" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -20393,7 +20077,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -20634,11 +20318,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A81" s="2" t="inlineStr"/>
       <c r="B81" s="2" t="inlineStr">
         <is>
           <t>111001100072</t>
@@ -20646,7 +20326,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED)</t>
+          <t>COLEGIO SANTIAGO DE LAS ATALAYAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
